--- a/results/0916-all/黔桂高原山地林农牧区/tech_selected_summary.xlsx
+++ b/results/0916-all/黔桂高原山地林农牧区/tech_selected_summary.xlsx
@@ -253,217 +253,217 @@
     <t>紫云苗族布依族自治县</t>
   </si>
   <si>
-    <t>县名</t>
-  </si>
-  <si>
-    <t>技术1</t>
-  </si>
-  <si>
-    <t>技术2</t>
-  </si>
-  <si>
-    <t>技术3</t>
-  </si>
-  <si>
-    <t>技术4</t>
-  </si>
-  <si>
-    <t>技术5</t>
-  </si>
-  <si>
-    <t>技术6</t>
-  </si>
-  <si>
-    <t>技术7</t>
-  </si>
-  <si>
-    <t>技术8</t>
-  </si>
-  <si>
-    <t>技术9</t>
-  </si>
-  <si>
-    <t>技术10</t>
-  </si>
-  <si>
-    <t>技术11</t>
-  </si>
-  <si>
-    <t>技术12</t>
-  </si>
-  <si>
-    <t>技术13</t>
-  </si>
-  <si>
-    <t>技术14</t>
-  </si>
-  <si>
-    <t>技术15</t>
-  </si>
-  <si>
-    <t>技术16</t>
-  </si>
-  <si>
-    <t>技术17</t>
-  </si>
-  <si>
-    <t>技术18</t>
-  </si>
-  <si>
-    <t>技术19</t>
-  </si>
-  <si>
-    <t>技术20</t>
-  </si>
-  <si>
-    <t>技术21</t>
-  </si>
-  <si>
-    <t>技术22</t>
-  </si>
-  <si>
-    <t>技术23</t>
-  </si>
-  <si>
-    <t>技术24</t>
-  </si>
-  <si>
-    <t>技术25</t>
-  </si>
-  <si>
-    <t>技术26</t>
-  </si>
-  <si>
-    <t>技术27</t>
-  </si>
-  <si>
-    <t>技术28</t>
-  </si>
-  <si>
-    <t>技术29</t>
-  </si>
-  <si>
-    <t>技术30</t>
-  </si>
-  <si>
-    <t>技术31</t>
-  </si>
-  <si>
-    <t>技术32</t>
-  </si>
-  <si>
-    <t>技术33</t>
-  </si>
-  <si>
-    <t>技术34</t>
-  </si>
-  <si>
-    <t>技术35</t>
-  </si>
-  <si>
-    <t>技术36</t>
-  </si>
-  <si>
-    <t>技术37</t>
-  </si>
-  <si>
-    <t>技术38</t>
-  </si>
-  <si>
-    <t>技术39</t>
-  </si>
-  <si>
-    <t>技术40</t>
-  </si>
-  <si>
-    <t>技术41</t>
-  </si>
-  <si>
-    <t>技术42</t>
-  </si>
-  <si>
-    <t>技术43</t>
-  </si>
-  <si>
-    <t>技术44</t>
-  </si>
-  <si>
-    <t>技术45</t>
-  </si>
-  <si>
-    <t>技术46</t>
-  </si>
-  <si>
-    <t>技术47</t>
-  </si>
-  <si>
-    <t>技术48</t>
-  </si>
-  <si>
-    <t>技术49</t>
-  </si>
-  <si>
-    <t>技术50</t>
-  </si>
-  <si>
-    <t>技术51</t>
-  </si>
-  <si>
-    <t>技术52</t>
-  </si>
-  <si>
-    <t>技术53</t>
-  </si>
-  <si>
-    <t>技术54</t>
-  </si>
-  <si>
-    <t>技术55</t>
-  </si>
-  <si>
-    <t>技术56</t>
-  </si>
-  <si>
-    <t>技术57</t>
-  </si>
-  <si>
-    <t>技术58</t>
-  </si>
-  <si>
-    <t>技术59</t>
-  </si>
-  <si>
-    <t>技术60</t>
-  </si>
-  <si>
-    <t>技术61</t>
-  </si>
-  <si>
-    <t>技术62</t>
-  </si>
-  <si>
-    <t>技术63</t>
-  </si>
-  <si>
-    <t>技术64</t>
-  </si>
-  <si>
-    <t>技术65</t>
-  </si>
-  <si>
-    <t>技术66</t>
-  </si>
-  <si>
-    <t>技术67</t>
-  </si>
-  <si>
-    <t>技术68</t>
-  </si>
-  <si>
-    <t>技术69</t>
-  </si>
-  <si>
-    <t>总经济成本</t>
+    <t>Counties</t>
+  </si>
+  <si>
+    <t>Tech1</t>
+  </si>
+  <si>
+    <t>Tech2</t>
+  </si>
+  <si>
+    <t>Tech3</t>
+  </si>
+  <si>
+    <t>Tech4</t>
+  </si>
+  <si>
+    <t>Tech5</t>
+  </si>
+  <si>
+    <t>Tech6</t>
+  </si>
+  <si>
+    <t>Tech7</t>
+  </si>
+  <si>
+    <t>Tech8</t>
+  </si>
+  <si>
+    <t>Tech9</t>
+  </si>
+  <si>
+    <t>Tech10</t>
+  </si>
+  <si>
+    <t>Tech11</t>
+  </si>
+  <si>
+    <t>Tech12</t>
+  </si>
+  <si>
+    <t>Tech13</t>
+  </si>
+  <si>
+    <t>Tech14</t>
+  </si>
+  <si>
+    <t>Tech15</t>
+  </si>
+  <si>
+    <t>Tech16</t>
+  </si>
+  <si>
+    <t>Tech17</t>
+  </si>
+  <si>
+    <t>Tech18</t>
+  </si>
+  <si>
+    <t>Tech19</t>
+  </si>
+  <si>
+    <t>Tech20</t>
+  </si>
+  <si>
+    <t>Tech21</t>
+  </si>
+  <si>
+    <t>Tech22</t>
+  </si>
+  <si>
+    <t>Tech23</t>
+  </si>
+  <si>
+    <t>Tech24</t>
+  </si>
+  <si>
+    <t>Tech25</t>
+  </si>
+  <si>
+    <t>Tech26</t>
+  </si>
+  <si>
+    <t>Tech27</t>
+  </si>
+  <si>
+    <t>Tech28</t>
+  </si>
+  <si>
+    <t>Tech29</t>
+  </si>
+  <si>
+    <t>Tech30</t>
+  </si>
+  <si>
+    <t>Tech31</t>
+  </si>
+  <si>
+    <t>Tech32</t>
+  </si>
+  <si>
+    <t>Tech33</t>
+  </si>
+  <si>
+    <t>Tech34</t>
+  </si>
+  <si>
+    <t>Tech35</t>
+  </si>
+  <si>
+    <t>Tech36</t>
+  </si>
+  <si>
+    <t>Tech37</t>
+  </si>
+  <si>
+    <t>Tech38</t>
+  </si>
+  <si>
+    <t>Tech39</t>
+  </si>
+  <si>
+    <t>Tech40</t>
+  </si>
+  <si>
+    <t>Tech41</t>
+  </si>
+  <si>
+    <t>Tech42</t>
+  </si>
+  <si>
+    <t>Tech43</t>
+  </si>
+  <si>
+    <t>Tech44</t>
+  </si>
+  <si>
+    <t>Tech45</t>
+  </si>
+  <si>
+    <t>Tech46</t>
+  </si>
+  <si>
+    <t>Tech47</t>
+  </si>
+  <si>
+    <t>Tech48</t>
+  </si>
+  <si>
+    <t>Tech49</t>
+  </si>
+  <si>
+    <t>Tech50</t>
+  </si>
+  <si>
+    <t>Tech51</t>
+  </si>
+  <si>
+    <t>Tech52</t>
+  </si>
+  <si>
+    <t>Tech53</t>
+  </si>
+  <si>
+    <t>Tech54</t>
+  </si>
+  <si>
+    <t>Tech55</t>
+  </si>
+  <si>
+    <t>Tech56</t>
+  </si>
+  <si>
+    <t>Tech57</t>
+  </si>
+  <si>
+    <t>Tech58</t>
+  </si>
+  <si>
+    <t>Tech59</t>
+  </si>
+  <si>
+    <t>Tech60</t>
+  </si>
+  <si>
+    <t>Tech61</t>
+  </si>
+  <si>
+    <t>Tech62</t>
+  </si>
+  <si>
+    <t>Tech63</t>
+  </si>
+  <si>
+    <t>Tech64</t>
+  </si>
+  <si>
+    <t>Tech65</t>
+  </si>
+  <si>
+    <t>Tech66</t>
+  </si>
+  <si>
+    <t>Tech67</t>
+  </si>
+  <si>
+    <t>Tech68</t>
+  </si>
+  <si>
+    <t>Tech69</t>
+  </si>
+  <si>
+    <t>Total economic cost</t>
   </si>
   <si>
     <t>Feed processing_dairy</t>
@@ -490,10 +490,10 @@
     <t>tillage management (zero tillage)_maize</t>
   </si>
   <si>
-    <t>总经济成本: 12812718.92</t>
-  </si>
-  <si>
-    <t>总经济成本: 0.00</t>
+    <t>12812718.92</t>
+  </si>
+  <si>
+    <t>0.00</t>
   </si>
   <si>
     <t>Increasing byproduct_pig</t>
@@ -598,25 +598,25 @@
     <t>irrigation (drip irrigation)_vegetable</t>
   </si>
   <si>
-    <t>总经济成本: 354047212.48</t>
+    <t>354047212.48</t>
   </si>
   <si>
     <t>EEF(CRF)_vegetable</t>
   </si>
   <si>
-    <t>总经济成本: 33235534.34</t>
-  </si>
-  <si>
-    <t>总经济成本: 7573542.15</t>
-  </si>
-  <si>
-    <t>总经济成本: 13871355.75</t>
+    <t>33235534.34</t>
+  </si>
+  <si>
+    <t>7573542.15</t>
+  </si>
+  <si>
+    <t>13871355.75</t>
   </si>
   <si>
     <t>Zeolite_pig</t>
   </si>
   <si>
-    <t>总经济成本: 10420232.14</t>
+    <t>10420232.14</t>
   </si>
   <si>
     <t>Yucca extract_Beef cattle</t>
@@ -625,28 +625,28 @@
     <t>irrigation (AWD irrigation)_rice</t>
   </si>
   <si>
-    <t>总经济成本: 47575109.93</t>
+    <t>47575109.93</t>
   </si>
   <si>
     <t>EEF(NI)_maize</t>
   </si>
   <si>
-    <t>总经济成本: 13449056.91</t>
+    <t>13449056.91</t>
   </si>
   <si>
     <t>residue rerention_maize</t>
   </si>
   <si>
-    <t>总经济成本: 42166703.53</t>
+    <t>42166703.53</t>
   </si>
   <si>
     <t>Plant-derived N substitution_maize</t>
   </si>
   <si>
-    <t>总经济成本: 294139802.11</t>
-  </si>
-  <si>
-    <t>总经济成本: 6711339.68</t>
+    <t>294139802.11</t>
+  </si>
+  <si>
+    <t>6711339.68</t>
   </si>
   <si>
     <t>Yucca extract_sheep &amp; goat</t>
@@ -730,13 +730,13 @@
     <t>irrigation (water-saving irrigation)_rice</t>
   </si>
   <si>
-    <t>总经济成本: 385380827.16</t>
-  </si>
-  <si>
-    <t>总经济成本: 121522541.31</t>
-  </si>
-  <si>
-    <t>总经济成本: 183519.88</t>
+    <t>385380827.16</t>
+  </si>
+  <si>
+    <t>121522541.31</t>
+  </si>
+  <si>
+    <t>183519.88</t>
   </si>
   <si>
     <t>chemical amendments_sheep&amp;goat</t>
@@ -745,10 +745,10 @@
     <t>Bioflilter_pig</t>
   </si>
   <si>
-    <t>总经济成本: 154880891.91</t>
-  </si>
-  <si>
-    <t>总经济成本: 4910938.43</t>
+    <t>154880891.91</t>
+  </si>
+  <si>
+    <t>4910938.43</t>
   </si>
   <si>
     <t>By-products source_beef cattle</t>
@@ -760,19 +760,19 @@
     <t>Adsorbent_poultry</t>
   </si>
   <si>
-    <t>总经济成本: 254440839.23</t>
+    <t>254440839.23</t>
   </si>
   <si>
     <t>incorporation_beef cattle</t>
   </si>
   <si>
-    <t>总经济成本: 150557923.96</t>
-  </si>
-  <si>
-    <t>总经济成本: 102399089.17</t>
-  </si>
-  <si>
-    <t>总经济成本: 19552325.07</t>
+    <t>150557923.96</t>
+  </si>
+  <si>
+    <t>102399089.17</t>
+  </si>
+  <si>
+    <t>19552325.07</t>
   </si>
   <si>
     <t>Increasing feeding level_sheep &amp; goat</t>
@@ -790,16 +790,16 @@
     <t>compost（add)_vegetable</t>
   </si>
   <si>
-    <t>总经济成本: 83269237.65</t>
-  </si>
-  <si>
-    <t>总经济成本: 6706280.90</t>
-  </si>
-  <si>
-    <t>总经济成本: 87626361.54</t>
-  </si>
-  <si>
-    <t>总经济成本: 42065937.05</t>
+    <t>83269237.65</t>
+  </si>
+  <si>
+    <t>6706280.90</t>
+  </si>
+  <si>
+    <t>87626361.54</t>
+  </si>
+  <si>
+    <t>42065937.05</t>
   </si>
   <si>
     <t>Slatted floor vs deep litter_pig</t>
@@ -811,58 +811,58 @@
     <t>compost（low）≤30%_maize</t>
   </si>
   <si>
-    <t>总经济成本: 814312122.60</t>
-  </si>
-  <si>
-    <t>总经济成本: 124208161.60</t>
-  </si>
-  <si>
-    <t>总经济成本: 13381.93</t>
-  </si>
-  <si>
-    <t>总经济成本: 4075582.25</t>
+    <t>814312122.60</t>
+  </si>
+  <si>
+    <t>124208161.60</t>
+  </si>
+  <si>
+    <t>13381.93</t>
+  </si>
+  <si>
+    <t>4075582.25</t>
   </si>
   <si>
     <t>Feedstock adjustment_dairy</t>
   </si>
   <si>
-    <t>总经济成本: 78550713.58</t>
+    <t>78550713.58</t>
   </si>
   <si>
     <t>cover crop (non-leguminous)_wheat</t>
   </si>
   <si>
-    <t>总经济成本: 132408460.68</t>
-  </si>
-  <si>
-    <t>总经济成本: 44044466.45</t>
-  </si>
-  <si>
-    <t>总经济成本: 265066485.38</t>
-  </si>
-  <si>
-    <t>总经济成本: 36248227.63</t>
+    <t>132408460.68</t>
+  </si>
+  <si>
+    <t>44044466.45</t>
+  </si>
+  <si>
+    <t>265066485.38</t>
+  </si>
+  <si>
+    <t>36248227.63</t>
   </si>
   <si>
     <t>nitrification inhibitor_sheep&amp;goat</t>
   </si>
   <si>
-    <t>总经济成本: 350831619.58</t>
-  </si>
-  <si>
-    <t>总经济成本: 20053417.48</t>
+    <t>350831619.58</t>
+  </si>
+  <si>
+    <t>20053417.48</t>
   </si>
   <si>
     <t>EEF(DI)_wheat</t>
   </si>
   <si>
-    <t>总经济成本: 234918360.50</t>
-  </si>
-  <si>
-    <t>总经济成本: 792536.47</t>
-  </si>
-  <si>
-    <t>总经济成本: 66751455.80</t>
+    <t>234918360.50</t>
+  </si>
+  <si>
+    <t>792536.47</t>
+  </si>
+  <si>
+    <t>66751455.80</t>
   </si>
   <si>
     <t>Chemical amendments_sheep&amp;goat</t>
@@ -871,7 +871,7 @@
     <t>biochar_maize</t>
   </si>
   <si>
-    <t>总经济成本: 494892819.77</t>
+    <t>494892819.77</t>
   </si>
   <si>
     <t>Decreasing grass maturity_beef cattle</t>
@@ -895,58 +895,58 @@
     <t>EEF(CRF)_wheat</t>
   </si>
   <si>
-    <t>总经济成本: 291708079.68</t>
-  </si>
-  <si>
-    <t>总经济成本: 286313264.91</t>
-  </si>
-  <si>
-    <t>总经济成本: 127005963.32</t>
-  </si>
-  <si>
-    <t>总经济成本: 143754154.73</t>
-  </si>
-  <si>
-    <t>总经济成本: 14830279.52</t>
-  </si>
-  <si>
-    <t>总经济成本: 22935505.75</t>
-  </si>
-  <si>
-    <t>总经济成本: 127286623.38</t>
-  </si>
-  <si>
-    <t>总经济成本: 244765603.96</t>
-  </si>
-  <si>
-    <t>总经济成本: 15773500.26</t>
+    <t>291708079.68</t>
+  </si>
+  <si>
+    <t>286313264.91</t>
+  </si>
+  <si>
+    <t>127005963.32</t>
+  </si>
+  <si>
+    <t>143754154.73</t>
+  </si>
+  <si>
+    <t>14830279.52</t>
+  </si>
+  <si>
+    <t>22935505.75</t>
+  </si>
+  <si>
+    <t>127286623.38</t>
+  </si>
+  <si>
+    <t>244765603.96</t>
+  </si>
+  <si>
+    <t>15773500.26</t>
   </si>
   <si>
     <t>artificial film cover_pig</t>
   </si>
   <si>
-    <t>总经济成本: 390727544.24</t>
-  </si>
-  <si>
-    <t>总经济成本: 110015114.35</t>
-  </si>
-  <si>
-    <t>总经济成本: 27721646.89</t>
-  </si>
-  <si>
-    <t>总经济成本: 49703828.75</t>
-  </si>
-  <si>
-    <t>总经济成本: 20311226.67</t>
-  </si>
-  <si>
-    <t>总经济成本: 110632371.02</t>
-  </si>
-  <si>
-    <t>总经济成本: 34839963.19</t>
-  </si>
-  <si>
-    <t>总经济成本: 57590892.61</t>
+    <t>390727544.24</t>
+  </si>
+  <si>
+    <t>110015114.35</t>
+  </si>
+  <si>
+    <t>27721646.89</t>
+  </si>
+  <si>
+    <t>49703828.75</t>
+  </si>
+  <si>
+    <t>20311226.67</t>
+  </si>
+  <si>
+    <t>110632371.02</t>
+  </si>
+  <si>
+    <t>34839963.19</t>
+  </si>
+  <si>
+    <t>57590892.61</t>
   </si>
 </sst>
 </file>
